--- a/data/trans_orig/P6713-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27347</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>32312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60917</t>
+          <t>61991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>84383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40659</t>
+          <t>40178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59379</t>
+          <t>59929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108449</t>
+          <t>109367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138403</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28649</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30217</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>34098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>28769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57561</t>
+          <t>58413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125922</t>
+          <t>126592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68857</t>
+          <t>69027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91393</t>
+          <t>90657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175418</t>
+          <t>175904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209756</t>
+          <t>211957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46259</t>
+          <t>45990</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45131</t>
+          <t>46275</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71201</t>
+          <t>71691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>47164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34827</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>58611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>54007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77231</t>
+          <t>77111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>49076</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92099</t>
+          <t>90984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121540</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52034</t>
+          <t>52327</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>25302</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>46527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37356</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49604</t>
+          <t>49117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78201</t>
+          <t>76436</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>57491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83394</t>
+          <t>83121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94081</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>126791</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32123</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50638</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46577</t>
+          <t>47709</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>71075</t>
+          <t>72040</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33016</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>26297</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>50268</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>32409</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>47609</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52376</t>
+          <t>52767</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>74948</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32937</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74010</t>
+          <t>73730</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>100873</t>
+          <t>101256</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>27116</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>45562</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>59099</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>90087</t>
+          <t>90254</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>65205</t>
+          <t>64856</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>104965</t>
+          <t>106950</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>145853</t>
+          <t>146899</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>63773</t>
+          <t>63251</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>57962</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>90015</t>
+          <t>90281</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>109322</t>
+          <t>105520</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>141947</t>
+          <t>140763</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>63750</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>89464</t>
+          <t>89750</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>178772</t>
+          <t>177889</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>220142</t>
+          <t>223252</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>69359</t>
+          <t>69264</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>103019</t>
+          <t>104189</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>35879</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>60657</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>113175</t>
+          <t>112896</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>154280</t>
+          <t>156653</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>107711</t>
+          <t>109551</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>146072</t>
+          <t>145983</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>74434</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>107491</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>194822</t>
+          <t>193402</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>244278</t>
+          <t>243419</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>98338</t>
+          <t>96708</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>134983</t>
+          <t>134923</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>77736</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>110757</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>185513</t>
+          <t>185928</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>232676</t>
+          <t>235553</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>76194</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>95795</t>
+          <t>95850</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>83273</t>
+          <t>80445</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>116612</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>166829</t>
+          <t>164835</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>258688</t>
+          <t>259390</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>324586</t>
+          <t>319812</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>173078</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>225076</t>
+          <t>224700</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>448801</t>
+          <t>449396</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>532615</t>
+          <t>530917</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>293788</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>358025</t>
+          <t>357649</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>173066</t>
+          <t>173052</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>223797</t>
+          <t>226030</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>480259</t>
+          <t>482769</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>567195</t>
+          <t>562307</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>628332</t>
+          <t>629882</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>706236</t>
+          <t>707062</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>391805</t>
+          <t>392031</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>456934</t>
+          <t>455033</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1041204</t>
+          <t>1040461</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1136814</t>
+          <t>1144728</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44935</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47278</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33020</t>
+          <t>34019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57494</t>
+          <t>58817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35116</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31165</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>58440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26598</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>45612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66067</t>
+          <t>65152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>97294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35131</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51586</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78314</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54258</t>
+          <t>53674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>44395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72682</t>
+          <t>70894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54907</t>
+          <t>54295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81246</t>
+          <t>79256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>35726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58220</t>
+          <t>56665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98099</t>
+          <t>95288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129683</t>
+          <t>129032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,47 +8632,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>26225</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>18196</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>36182</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>8,64%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>26225</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>18006</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>35437</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>31146</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>50489</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26691</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>46937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>70767</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44884</t>
+          <t>45623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23635</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40962</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81367</t>
+          <t>80541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22571</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22126</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59481</t>
+          <t>57500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27381</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34283</t>
+          <t>34922</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33004</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62878</t>
+          <t>63006</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83527</t>
+          <t>83733</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33092</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50809</t>
+          <t>51936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>100177</t>
+          <t>101053</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127776</t>
+          <t>129957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27605</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51327</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30512</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>48311</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32521</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50171</t>
+          <t>51607</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74252</t>
+          <t>74275</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34135</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -10515,97 +10515,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>6169</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>1779</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>6344</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>6089</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1779</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>5626</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>49158</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>52454</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77590</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38328</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>59638</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31329</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>40537</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>43474</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>44351</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>73600</t>
+          <t>74973</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28965</t>
+          <t>29700</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>56450</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>52069</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>66000</t>
+          <t>65263</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>100236</t>
+          <t>98880</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>97206</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>133764</t>
+          <t>134556</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>72015</t>
+          <t>70460</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>102593</t>
+          <t>101514</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>175756</t>
+          <t>175662</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>225208</t>
+          <t>228250</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>56731</t>
+          <t>56931</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>89289</t>
+          <t>88659</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>40630</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>64555</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>103479</t>
+          <t>103572</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>146943</t>
+          <t>145820</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>85007</t>
+          <t>84467</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>122207</t>
+          <t>121032</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>61494</t>
+          <t>62780</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>93210</t>
+          <t>93121</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>158366</t>
+          <t>156870</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>205181</t>
+          <t>203020</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>33000</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>27395</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>47375</t>
+          <t>48875</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>78904</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>77078</t>
+          <t>77737</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>115093</t>
+          <t>113814</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>98176</t>
+          <t>96304</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>130616</t>
+          <t>130388</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>81817</t>
+          <t>83304</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>113687</t>
+          <t>114555</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>186676</t>
+          <t>189557</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>233063</t>
+          <t>236224</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105464</t>
+          <t>106249</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>143025</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>63776</t>
+          <t>62921</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>93195</t>
+          <t>93709</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>179996</t>
+          <t>179902</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>226312</t>
+          <t>225089</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>63831</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>101431</t>
+          <t>102604</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>73965</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>110892</t>
+          <t>109459</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>146978</t>
+          <t>148285</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>199217</t>
+          <t>196159</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>162466</t>
+          <t>161761</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>106431</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>148650</t>
+          <t>150378</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>237554</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>300488</t>
+          <t>296757</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>327380</t>
+          <t>325332</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>391865</t>
+          <t>393512</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>202857</t>
+          <t>205956</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>259802</t>
+          <t>261059</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>546345</t>
+          <t>543659</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>632491</t>
+          <t>633200</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>327511</t>
+          <t>332091</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>397596</t>
+          <t>397521</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>245695</t>
+          <t>248417</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>302439</t>
+          <t>303396</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>593072</t>
+          <t>596597</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>682836</t>
+          <t>685202</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>444873</t>
+          <t>447229</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>518906</t>
+          <t>520952</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>287597</t>
+          <t>283995</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>344681</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>749019</t>
+          <t>749016</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>844109</t>
+          <t>844967</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6713-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27217</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49270</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>26947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>14222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32312</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61991</t>
+          <t>61435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84383</t>
+          <t>84836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59929</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109367</t>
+          <t>107833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138415</t>
+          <t>138003</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29674</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58413</t>
+          <t>57894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100136</t>
+          <t>100029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126592</t>
+          <t>124994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>68522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90657</t>
+          <t>90825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175904</t>
+          <t>175570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211957</t>
+          <t>209790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,13%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45990</t>
+          <t>46481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46275</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47164</t>
+          <t>46760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19220</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58611</t>
+          <t>60162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54007</t>
+          <t>53769</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77111</t>
+          <t>76375</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31172</t>
+          <t>30130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90984</t>
+          <t>90256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119966</t>
+          <t>119172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23483</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>28426</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>31455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>51588</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25302</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46527</t>
+          <t>45604</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38421</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>47249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76436</t>
+          <t>77412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57491</t>
+          <t>58664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83121</t>
+          <t>84548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>30678</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50951</t>
+          <t>51251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94238</t>
+          <t>94802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>127862</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39477</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>31576</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32374</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>50693</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47709</t>
+          <t>48069</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>71823</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,46%</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32604</t>
+          <t>32661</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>32409</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>48355</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>52105</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>74948</t>
+          <t>74566</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>74194</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>101256</t>
+          <t>100328</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>45876</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>59099</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>90254</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>40004</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>64856</t>
+          <t>65684</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>106950</t>
+          <t>107742</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>146899</t>
+          <t>146794</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>37020</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>63251</t>
+          <t>62667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>57962</t>
+          <t>60055</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>90281</t>
+          <t>89982</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>105520</t>
+          <t>106745</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>140763</t>
+          <t>139962</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>63750</t>
+          <t>62096</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>89750</t>
+          <t>88836</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>177889</t>
+          <t>178215</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>223252</t>
+          <t>220903</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,47 +5555,47 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>24969</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>16187</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>38121</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>24969</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>16486</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>37519</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>34798</t>
+          <t>35483</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22543</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>48272</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>69264</t>
+          <t>69899</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>104189</t>
+          <t>103325</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>35879</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>61598</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>112896</t>
+          <t>113857</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>156653</t>
+          <t>153964</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>109551</t>
+          <t>109601</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>145983</t>
+          <t>145348</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>74434</t>
+          <t>75434</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>107491</t>
+          <t>108551</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>193402</t>
+          <t>195276</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>243419</t>
+          <t>245395</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>96708</t>
+          <t>98462</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>134923</t>
+          <t>134511</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>77257</t>
+          <t>78118</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>110757</t>
+          <t>110428</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>185928</t>
+          <t>185226</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>235553</t>
+          <t>233530</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>96706</t>
+          <t>99184</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>139908</t>
+          <t>143265</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>95850</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>80445</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>114879</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>164835</t>
+          <t>165514</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>259390</t>
+          <t>257683</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>319812</t>
+          <t>321132</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>174840</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>224700</t>
+          <t>227362</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>449396</t>
+          <t>443412</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>530917</t>
+          <t>529327</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>293432</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>357649</t>
+          <t>356761</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>173052</t>
+          <t>174130</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>226030</t>
+          <t>225532</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>482769</t>
+          <t>483511</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>562307</t>
+          <t>568824</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>629882</t>
+          <t>623768</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>707062</t>
+          <t>701651</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>392031</t>
+          <t>391152</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>455033</t>
+          <t>453425</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1040461</t>
+          <t>1032744</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1144728</t>
+          <t>1139157</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45333</t>
+          <t>46483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33117</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45979</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>36393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27747</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>57289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34350</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30374</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>33965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58440</t>
+          <t>60237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>57838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>45417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>65910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97294</t>
+          <t>95557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36828</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52266</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>51003</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78290</t>
+          <t>78101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>31099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53674</t>
+          <t>54025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44395</t>
+          <t>43979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>71469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54295</t>
+          <t>53774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79256</t>
+          <t>79970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35726</t>
+          <t>35022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95288</t>
+          <t>96245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129032</t>
+          <t>130472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36182</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50489</t>
+          <t>50440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46937</t>
+          <t>47148</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70767</t>
+          <t>71891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45623</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80541</t>
+          <t>80161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>34969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57500</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>26775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13468</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>32934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>61083</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83733</t>
+          <t>83235</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51936</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101053</t>
+          <t>100673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129957</t>
+          <t>128647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51228</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32043</t>
+          <t>30997</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74275</t>
+          <t>74560</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>33782</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>49673</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45381</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>37099</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>52454</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77455</t>
+          <t>77360</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>39247</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>25479</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>35617</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>59303</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43474</t>
+          <t>41980</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>74973</t>
+          <t>74614</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>56450</t>
+          <t>54980</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>52247</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>65263</t>
+          <t>65681</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>99915</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>97946</t>
+          <t>96359</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>134556</t>
+          <t>134038</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>70460</t>
+          <t>72118</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>101514</t>
+          <t>103578</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>175662</t>
+          <t>177825</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>228250</t>
+          <t>229023</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>56931</t>
+          <t>58557</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>88659</t>
+          <t>89202</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>40630</t>
+          <t>39608</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>67459</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>103572</t>
+          <t>104363</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>145820</t>
+          <t>148038</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>84467</t>
+          <t>85740</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>121032</t>
+          <t>123926</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>62780</t>
+          <t>62611</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>93121</t>
+          <t>91989</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>156870</t>
+          <t>155312</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>203020</t>
+          <t>203376</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26334</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>51785</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>48875</t>
+          <t>47710</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>78904</t>
+          <t>76847</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>77737</t>
+          <t>77852</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>113835</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>96304</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>130388</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>83304</t>
+          <t>82835</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>114555</t>
+          <t>114179</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>189557</t>
+          <t>189732</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>236224</t>
+          <t>235254</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>106249</t>
+          <t>104874</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>143025</t>
+          <t>141726</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>62921</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>93709</t>
+          <t>94963</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>179902</t>
+          <t>179491</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>225089</t>
+          <t>225185</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>63831</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>102604</t>
+          <t>101795</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>73450</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>109459</t>
+          <t>111489</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>148285</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>196159</t>
+          <t>197846</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>161761</t>
+          <t>159448</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>108633</t>
+          <t>107398</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>150378</t>
+          <t>148753</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>232820</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>296757</t>
+          <t>296368</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>325332</t>
+          <t>323701</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>393512</t>
+          <t>388731</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>205956</t>
+          <t>204902</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>261059</t>
+          <t>256757</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>543659</t>
+          <t>548109</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>633200</t>
+          <t>635571</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>332091</t>
+          <t>331235</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>397521</t>
+          <t>398886</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>248417</t>
+          <t>246418</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>303396</t>
+          <t>301678</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>596597</t>
+          <t>593924</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>685202</t>
+          <t>681850</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>447229</t>
+          <t>444076</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>520952</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>283995</t>
+          <t>285770</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>344400</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>749016</t>
+          <t>748429</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>844967</t>
+          <t>842989</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
